--- a/jpcore-r4/develop-kohetest/StructureDefinition-jp-medicationdosage.xlsx
+++ b/jpcore-r4/develop-kohetest/StructureDefinition-jp-medicationdosage.xlsx
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationDosageBase</t>
+    <t>http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationDosageBase|1.3.0-dev</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -331,7 +331,7 @@
     <t>periodOfUse</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDosage_PeriodOfUse}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDosage_PeriodOfUse|1.3.0-dev}
 </t>
   </si>
   <si>
@@ -347,7 +347,7 @@
     <t>usageDuration</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDosage_UsageDuration}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDosage_UsageDuration|1.3.0-dev}
 </t>
   </si>
   <si>
@@ -449,7 +449,7 @@
     <t>preferred</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationUsageJAMIAdditional_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationUsageJAMIAdditional_VS|1.1.0a</t>
   </si>
   <si>
     <t>RXO-7</t>
@@ -470,7 +470,7 @@
     <t>Dosage.timing</t>
   </si>
   <si>
-    <t xml:space="preserve">Timing {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationTiming}
+    <t xml:space="preserve">Timing {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationTiming|1.3.0-dev}
 </t>
   </si>
   <si>
@@ -1010,7 +1010,7 @@
 【JP Core仕様】JAMI標準用法コード(16桁)を使用することが望ましいが、ローカルコードも使用可能。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationUsageJAMI_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationUsageJAMI_VS|1.1.0a</t>
   </si>
   <si>
     <t>Timing.code</t>
@@ -1058,7 +1058,7 @@
     <t>薬が最初に体に入る解剖学的部位のコード化された仕様。 / A coded specification of the anatomic site where the medication first enters the body.</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationBodySiteJAMIExternal_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationBodySiteJAMIExternal_VS|1.1.0a</t>
   </si>
   <si>
     <t>.approachSiteCode</t>
@@ -1080,7 +1080,7 @@
     <t>患者の体への、または患者の体内への治療剤の投与のルートまたは生理学的経路を指定するコード。 / A code specifying the route or physiological path of administration of a therapeutic agent into or onto a patient's body.</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationRouteHL70162_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationRouteHL70162_VS|1.2.0</t>
   </si>
   <si>
     <t>.routeCode</t>
@@ -1107,7 +1107,7 @@
     <t>薬が投与される手法を説明するコード化された概念。 / A coded concept describing the technique by which the medicine is administered.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/administration-method-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/administration-method-codes|4.0.1</t>
   </si>
   <si>
     <t>.doseQuantity</t>
@@ -1172,7 +1172,7 @@
     <t>他のコードシステムへの変換や代替のコードシステムを使ってエンコードしてもよい。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationMethodJAMIBasicUsage_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationMethodJAMIBasicUsage_VS|1.1.0a</t>
   </si>
   <si>
     <t>Dosage.method.coding:unitDigit1.id</t>
@@ -1328,7 +1328,7 @@
     <t>投与⽅法に対応するJAMI 用法コード表基本用法2桁コードを識別するURI。２桁コードhttp://jami.jp/CodeSystem/MedicationUsage</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationMethodJAMIDetailUsage_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationMethodJAMIDetailUsage_VS|1.1.0a</t>
   </si>
   <si>
     <t>Dosage.method.coding:unitDigit2.id</t>
@@ -1397,7 +1397,7 @@
     <t>このtypeに値が指定されていなければ、"ordered"であることが想定される。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationIngredientStrengthStrengthType_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationIngredientStrengthStrengthType_VS|1.1.0a</t>
   </si>
   <si>
     <t>RXO-21; RXE-23</t>
@@ -1406,7 +1406,7 @@
     <t>Dosage.doseAndRate.dose[x]</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationSimpleQuantity}
+    <t xml:space="preserve">Quantity {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationSimpleQuantity|1.3.0-dev}
 </t>
   </si>
   <si>
@@ -1427,7 +1427,7 @@
   </si>
   <si>
     <t>Ratio
-RangeQuantity {SimpleQuantity}</t>
+RangeQuantity {SimpleQuantity|4.0.1}</t>
   </si>
   <si>
     <t>薬剤の投与量速度</t>
@@ -1461,7 +1461,7 @@
     <t>rateRatio</t>
   </si>
   <si>
-    <t xml:space="preserve">Ratio {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRatio_DosePerDay}
+    <t xml:space="preserve">Ratio {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRatio_DosePerDay|1.3.0-dev}
 </t>
   </si>
   <si>
@@ -1471,7 +1471,7 @@
     <t>rateRange</t>
   </si>
   <si>
-    <t xml:space="preserve">Range {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRange_UnitOfTime}
+    <t xml:space="preserve">Range {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRange_UnitOfTime|1.3.0-dev}
 </t>
   </si>
   <si>
@@ -1481,7 +1481,7 @@
     <t>rateQuantity</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -1491,7 +1491,7 @@
     <t>Dosage.maxDosePerPeriod</t>
   </si>
   <si>
-    <t xml:space="preserve">Ratio {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRatio_DosePerPeriod}
+    <t xml:space="preserve">Ratio {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRatio_DosePerPeriod|1.3.0-dev}
 </t>
   </si>
   <si>
@@ -1848,7 +1848,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="82.5390625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="90.53125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1863,7 +1863,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="89.67578125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="66.17578125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="71.66796875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/jpcore-r4/develop-kohetest/StructureDefinition-jp-medicationdosage.xlsx
+++ b/jpcore-r4/develop-kohetest/StructureDefinition-jp-medicationdosage.xlsx
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationDosageBase|1.3.0-dev</t>
+    <t>http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationDosageBase</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -331,7 +331,7 @@
     <t>periodOfUse</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDosage_PeriodOfUse|1.3.0-dev}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDosage_PeriodOfUse}
 </t>
   </si>
   <si>
@@ -347,7 +347,7 @@
     <t>usageDuration</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDosage_UsageDuration|1.3.0-dev}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDosage_UsageDuration}
 </t>
   </si>
   <si>
@@ -449,7 +449,7 @@
     <t>preferred</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationUsageJAMIAdditional_VS|1.1.0a</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationUsageJAMIAdditional_VS</t>
   </si>
   <si>
     <t>RXO-7</t>
@@ -470,7 +470,7 @@
     <t>Dosage.timing</t>
   </si>
   <si>
-    <t xml:space="preserve">Timing {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationTiming|1.3.0-dev}
+    <t xml:space="preserve">Timing {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationTiming}
 </t>
   </si>
   <si>
@@ -1010,7 +1010,7 @@
 【JP Core仕様】JAMI標準用法コード(16桁)を使用することが望ましいが、ローカルコードも使用可能。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationUsageJAMI_VS|1.1.0a</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationUsageJAMI_VS</t>
   </si>
   <si>
     <t>Timing.code</t>
@@ -1058,7 +1058,7 @@
     <t>薬が最初に体に入る解剖学的部位のコード化された仕様。 / A coded specification of the anatomic site where the medication first enters the body.</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationBodySiteJAMIExternal_VS|1.1.0a</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationBodySiteJAMIExternal_VS</t>
   </si>
   <si>
     <t>.approachSiteCode</t>
@@ -1080,7 +1080,7 @@
     <t>患者の体への、または患者の体内への治療剤の投与のルートまたは生理学的経路を指定するコード。 / A code specifying the route or physiological path of administration of a therapeutic agent into or onto a patient's body.</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationRouteHL70162_VS|1.2.0</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationRouteHL70162_VS</t>
   </si>
   <si>
     <t>.routeCode</t>
@@ -1107,7 +1107,7 @@
     <t>薬が投与される手法を説明するコード化された概念。 / A coded concept describing the technique by which the medicine is administered.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/administration-method-codes|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/administration-method-codes</t>
   </si>
   <si>
     <t>.doseQuantity</t>
@@ -1172,7 +1172,7 @@
     <t>他のコードシステムへの変換や代替のコードシステムを使ってエンコードしてもよい。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationMethodJAMIBasicUsage_VS|1.1.0a</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationMethodJAMIBasicUsage_VS</t>
   </si>
   <si>
     <t>Dosage.method.coding:unitDigit1.id</t>
@@ -1328,7 +1328,7 @@
     <t>投与⽅法に対応するJAMI 用法コード表基本用法2桁コードを識別するURI。２桁コードhttp://jami.jp/CodeSystem/MedicationUsage</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationMethodJAMIDetailUsage_VS|1.1.0a</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationMethodJAMIDetailUsage_VS</t>
   </si>
   <si>
     <t>Dosage.method.coding:unitDigit2.id</t>
@@ -1397,7 +1397,7 @@
     <t>このtypeに値が指定されていなければ、"ordered"であることが想定される。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationIngredientStrengthStrengthType_VS|1.1.0a</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationIngredientStrengthStrengthType_VS</t>
   </si>
   <si>
     <t>RXO-21; RXE-23</t>
@@ -1406,7 +1406,7 @@
     <t>Dosage.doseAndRate.dose[x]</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationSimpleQuantity|1.3.0-dev}
+    <t xml:space="preserve">Quantity {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationSimpleQuantity}
 </t>
   </si>
   <si>
@@ -1427,7 +1427,7 @@
   </si>
   <si>
     <t>Ratio
-RangeQuantity {SimpleQuantity|4.0.1}</t>
+RangeQuantity {SimpleQuantity}</t>
   </si>
   <si>
     <t>薬剤の投与量速度</t>
@@ -1461,7 +1461,7 @@
     <t>rateRatio</t>
   </si>
   <si>
-    <t xml:space="preserve">Ratio {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRatio_DosePerDay|1.3.0-dev}
+    <t xml:space="preserve">Ratio {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRatio_DosePerDay}
 </t>
   </si>
   <si>
@@ -1471,7 +1471,7 @@
     <t>rateRange</t>
   </si>
   <si>
-    <t xml:space="preserve">Range {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRange_UnitOfTime|1.3.0-dev}
+    <t xml:space="preserve">Range {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRange_UnitOfTime}
 </t>
   </si>
   <si>
@@ -1481,7 +1481,7 @@
     <t>rateQuantity</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
+    <t xml:space="preserve">Quantity {SimpleQuantity}
 </t>
   </si>
   <si>
@@ -1491,7 +1491,7 @@
     <t>Dosage.maxDosePerPeriod</t>
   </si>
   <si>
-    <t xml:space="preserve">Ratio {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRatio_DosePerPeriod|1.3.0-dev}
+    <t xml:space="preserve">Ratio {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRatio_DosePerPeriod}
 </t>
   </si>
   <si>
@@ -1848,7 +1848,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="90.53125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="82.5390625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1863,7 +1863,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="89.67578125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="71.66796875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="66.17578125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
